--- a/test-ecommerce-orders.xlsx
+++ b/test-ecommerce-orders.xlsx
@@ -3,11 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="抖音-销售订单明细" sheetId="1" r:id="rId1"/>
-    <sheet name="快手-销售订单明细" sheetId="2" r:id="rId2"/>
-    <sheet name="视频号-销售订单明细" sheetId="3" r:id="rId3"/>
-    <sheet name="抖店-售后订单" sheetId="4" r:id="rId4"/>
-    <sheet name="快手-售后订单" sheetId="5" r:id="rId5"/>
+    <sheet name="抖音销售订单" sheetId="1" r:id="rId1"/>
+    <sheet name="快手销售订单" sheetId="2" r:id="rId2"/>
+    <sheet name="视频号销售订单" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -401,14 +399,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:W34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>售后订单</v>
+        <v>序号</v>
       </c>
       <c r="B1" t="str">
-        <v>差异</v>
+        <v>商品明细</v>
       </c>
       <c r="C1" t="str">
         <v>支付完成时间</v>
@@ -417,22 +415,22 @@
         <v>店铺</v>
       </c>
       <c r="E1" t="str">
-        <v>主订单编号</v>
+        <v>父订单编号</v>
       </c>
       <c r="F1" t="str">
         <v>子订单编号</v>
       </c>
       <c r="G1" t="str">
-        <v>支付方式</v>
+        <v>商家订单编号</v>
       </c>
       <c r="H1" t="str">
-        <v>选购商品</v>
+        <v>售后状态</v>
       </c>
       <c r="I1" t="str">
-        <v>货号</v>
+        <v>发货方式</v>
       </c>
       <c r="J1" t="str">
-        <v>商品ID</v>
+        <v>物流单号</v>
       </c>
       <c r="K1" t="str">
         <v>商家编码</v>
@@ -444,57 +442,54 @@
         <v>商品金额</v>
       </c>
       <c r="N1" t="str">
-        <v/>
+        <v>售后备注</v>
       </c>
       <c r="O1" t="str">
-        <v/>
+        <v>收货人</v>
       </c>
       <c r="P1" t="str">
-        <v/>
+        <v>联系电话</v>
       </c>
       <c r="Q1" t="str">
-        <v/>
+        <v>收货地址</v>
       </c>
       <c r="R1" t="str">
-        <v/>
+        <v>省份</v>
       </c>
       <c r="S1" t="str">
-        <v/>
+        <v>城市</v>
       </c>
       <c r="T1" t="str">
-        <v/>
+        <v>区县</v>
       </c>
       <c r="U1" t="str">
-        <v/>
+        <v>订单备注</v>
       </c>
       <c r="V1" t="str">
-        <v/>
+        <v>修改时间</v>
       </c>
       <c r="W1" t="str">
-        <v/>
-      </c>
-      <c r="X1" t="str">
         <v>订单状态</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>2026-03-26 00:00:00</v>
+        <v>2026-03-26 08:53:57</v>
       </c>
       <c r="D2" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-靓仔甄选台球店</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>PDD20260326085357000</v>
       </c>
       <c r="F2" t="str">
-        <v>6951598266728256762</v>
+        <v>DD20260326085357000</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -503,40 +498,40 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>DAD005</v>
+        <v>TB001</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>152</v>
+        <v>768</v>
       </c>
       <c r="N2" t="str">
         <v/>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U2" t="str">
         <v/>
@@ -545,27 +540,27 @@
         <v/>
       </c>
       <c r="W2" t="str">
-        <v>待发货</v>
+        <v>已完成</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v/>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>2026-03-21 00:00:00</v>
+        <v>2026-03-26 08:53:57</v>
       </c>
       <c r="D3" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-台球four号店</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>PDD20260326085357001</v>
       </c>
       <c r="F3" t="str">
-        <v>6951455191353202176</v>
+        <v>DD20260326085357001</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -574,40 +569,40 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>DAD003</v>
+        <v>TA163</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1000</v>
+        <v>899</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U3" t="str">
         <v/>
@@ -616,27 +611,27 @@
         <v/>
       </c>
       <c r="W3" t="str">
-        <v>已发货</v>
+        <v>已完成</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v/>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>2026-03-21 00:00:00</v>
+        <v>2026-03-26 08:53:57</v>
       </c>
       <c r="D4" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-好事情台球</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>PDD20260326085357002</v>
       </c>
       <c r="F4" t="str">
-        <v>6951455136509924864</v>
+        <v>DD20260326085357002</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -645,40 +640,40 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>DAD003</v>
+        <v>TA163</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1000</v>
+        <v>921</v>
       </c>
       <c r="N4" t="str">
         <v/>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R4" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S4" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U4" t="str">
         <v/>
@@ -691,23 +686,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v/>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>2026-03-16 00:00:00</v>
+        <v>2026-03-27 14:31:02</v>
       </c>
       <c r="D5" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-靓仔甄选台球店</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>PDD20260327143102000</v>
       </c>
       <c r="F5" t="str">
-        <v>6924932537567509876</v>
+        <v>DD20260327143102000</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -716,40 +711,40 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>DAB002</v>
+        <v>TA013</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>1000</v>
+        <v>735</v>
       </c>
       <c r="N5" t="str">
         <v/>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R5" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S5" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T5" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U5" t="str">
         <v/>
@@ -762,23 +757,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v/>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>2026-03-15 00:00:00</v>
+        <v>2026-03-27 14:31:02</v>
       </c>
       <c r="D6" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-好事情台球</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>PDD20260327143102001</v>
       </c>
       <c r="F6" t="str">
-        <v>6951326852869330473</v>
+        <v>DD20260327143102001</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -787,40 +782,40 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>DAD011</v>
+        <v>TA170</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>189</v>
+        <v>776</v>
       </c>
       <c r="N6" t="str">
         <v/>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R6" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S6" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T6" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U6" t="str">
         <v/>
@@ -833,23 +828,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v/>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>2026-03-13 00:00:00</v>
+        <v>2026-03-27 14:31:02</v>
       </c>
       <c r="D7" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-台球four号店</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>PDD20260327143102002</v>
       </c>
       <c r="F7" t="str">
-        <v>6951290930719561004</v>
+        <v>DD20260327143102002</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -858,40 +853,40 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>DAD003</v>
+        <v>DAB002</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>249</v>
       </c>
       <c r="N7" t="str">
         <v/>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R7" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S7" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T7" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U7" t="str">
         <v/>
@@ -904,23 +899,23 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v/>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>2026-03-13 00:00:00</v>
+        <v>2026-03-27 14:31:02</v>
       </c>
       <c r="D8" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-好事情台球</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>PDD20260327143102003</v>
       </c>
       <c r="F8" t="str">
-        <v>6951269632575804533</v>
+        <v>DD20260327143102003</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -929,40 +924,40 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>DAD011</v>
+        <v>DAB002</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="N8" t="str">
         <v/>
       </c>
       <c r="O8" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R8" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S8" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T8" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U8" t="str">
         <v/>
@@ -971,27 +966,27 @@
         <v/>
       </c>
       <c r="W8" t="str">
-        <v>已完成</v>
+        <v>待发货</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v/>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>2026-03-11 00:00:00</v>
+        <v>2026-03-27 14:31:02</v>
       </c>
       <c r="D9" t="str">
-        <v>抖店-王孟南台球教学店</v>
+        <v>抖店-台球four号店</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>PDD20260327143102004</v>
       </c>
       <c r="F9" t="str">
-        <v>6951229996072768715</v>
+        <v>DD20260327143102004</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -1000,40 +995,40 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>TB001</v>
+        <v>TA175</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
       <c r="M9">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="N9" t="str">
         <v/>
       </c>
       <c r="O9" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R9" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S9" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T9" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U9" t="str">
         <v/>
@@ -1046,23 +1041,23 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v/>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-27 14:31:02</v>
       </c>
       <c r="D10" t="str">
         <v>抖店-靓仔甄选台球店</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>PDD20260327143102005</v>
       </c>
       <c r="F10" t="str">
-        <v>6951362052576056790</v>
+        <v>DD20260327143102005</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1071,40 +1066,40 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>TA163</v>
+        <v>DAB002</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>1280</v>
+        <v>917</v>
       </c>
       <c r="N10" t="str">
         <v/>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R10" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S10" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T10" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U10" t="str">
         <v/>
@@ -1117,23 +1112,23 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v/>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-28 10:07:58</v>
       </c>
       <c r="D11" t="str">
-        <v>抖店-靓仔甄选台球店</v>
+        <v>抖店-好事情台球</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>PDD20260328100758000</v>
       </c>
       <c r="F11" t="str">
-        <v>6951344171197863250</v>
+        <v>DD20260328100758000</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1142,40 +1137,40 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>TA163</v>
+        <v>DAD011</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>1280</v>
+        <v>471</v>
       </c>
       <c r="N11" t="str">
         <v/>
       </c>
       <c r="O11" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R11" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S11" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T11" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U11" t="str">
         <v/>
@@ -1188,23 +1183,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v/>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-28 10:07:58</v>
       </c>
       <c r="D12" t="str">
         <v>抖店-靓仔甄选台球店</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>PDD20260328100758001</v>
       </c>
       <c r="F12" t="str">
-        <v>6924924171016175421</v>
+        <v>DD20260328100758001</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1213,40 +1208,40 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>TA163</v>
+        <v>DAD005</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>1280</v>
+        <v>517</v>
       </c>
       <c r="N12" t="str">
         <v/>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R12" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S12" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T12" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U12" t="str">
         <v/>
@@ -1259,23 +1254,23 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v/>
+      <c r="A13">
+        <v>12</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-28 10:07:58</v>
       </c>
       <c r="D13" t="str">
         <v>抖店-靓仔甄选台球店</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>PDD20260328100758002</v>
       </c>
       <c r="F13" t="str">
-        <v>6951335301191112443</v>
+        <v>DD20260328100758002</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1284,40 +1279,40 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>TA013</v>
+        <v>DAD011</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
       <c r="M13">
-        <v>1980</v>
+        <v>525</v>
       </c>
       <c r="N13" t="str">
         <v/>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R13" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S13" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T13" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U13" t="str">
         <v/>
@@ -1326,27 +1321,27 @@
         <v/>
       </c>
       <c r="W13" t="str">
-        <v>已完成</v>
+        <v>待发货</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v/>
+      <c r="A14">
+        <v>13</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-28 10:07:58</v>
       </c>
       <c r="D14" t="str">
-        <v>抖店-靓仔甄选台球店</v>
+        <v>抖店-台球four号店</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>PDD20260328100758003</v>
       </c>
       <c r="F14" t="str">
-        <v>6924917684659650073</v>
+        <v>DD20260328100758003</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1355,40 +1350,40 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>TA013</v>
+        <v>DAB002</v>
       </c>
       <c r="L14">
         <v>1</v>
       </c>
       <c r="M14">
-        <v>1980</v>
+        <v>616</v>
       </c>
       <c r="N14" t="str">
         <v/>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R14" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S14" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T14" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U14" t="str">
         <v/>
@@ -1401,23 +1396,23 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v/>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-29 14:39:58</v>
       </c>
       <c r="D15" t="str">
-        <v>抖店-靓仔甄选台球店</v>
+        <v>抖店-王孟南台球教学店</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>PDD20260329143958000</v>
       </c>
       <c r="F15" t="str">
-        <v>6951366311652366080</v>
+        <v>DD20260329143958000</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1426,40 +1421,40 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>TA013</v>
+        <v>DAB002</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>1980</v>
+        <v>714</v>
       </c>
       <c r="N15" t="str">
         <v/>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R15" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S15" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T15" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U15" t="str">
         <v/>
@@ -1472,23 +1467,23 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v/>
+      <c r="A16">
+        <v>15</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-29 14:39:58</v>
       </c>
       <c r="D16" t="str">
-        <v>抖店-靓仔甄选台球店</v>
+        <v>抖店-台球four号店</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>PDD20260329143958001</v>
       </c>
       <c r="F16" t="str">
-        <v>6924915386441039289</v>
+        <v>DD20260329143958001</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1497,7 +1492,7 @@
         <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1509,28 +1504,28 @@
         <v>1</v>
       </c>
       <c r="M16">
-        <v>1980</v>
+        <v>142</v>
       </c>
       <c r="N16" t="str">
         <v/>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R16" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S16" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T16" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U16" t="str">
         <v/>
@@ -1539,27 +1534,27 @@
         <v/>
       </c>
       <c r="W16" t="str">
-        <v>已完成</v>
+        <v>已发货</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v/>
+      <c r="A17">
+        <v>16</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-29 14:39:58</v>
       </c>
       <c r="D17" t="str">
-        <v>抖店-靓仔甄选台球店</v>
+        <v>抖店-好事情台球</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>PDD20260329143958002</v>
       </c>
       <c r="F17" t="str">
-        <v>6951339865717806294</v>
+        <v>DD20260329143958002</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1568,40 +1563,40 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>TA013</v>
+        <v>DAB002</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
       <c r="M17">
-        <v>1980</v>
+        <v>131</v>
       </c>
       <c r="N17" t="str">
         <v/>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R17" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S17" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T17" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U17" t="str">
         <v/>
@@ -1614,23 +1609,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v/>
+      <c r="A18">
+        <v>17</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-30 09:33:27</v>
       </c>
       <c r="D18" t="str">
-        <v>抖店-靓仔甄选台球店</v>
+        <v>抖店-好事情台球</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>PDD20260330093327000</v>
       </c>
       <c r="F18" t="str">
-        <v>6924928518619168636</v>
+        <v>DD20260330093327000</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1639,40 +1634,40 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>TA013</v>
+        <v>TA170</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18">
-        <v>1980</v>
+        <v>369</v>
       </c>
       <c r="N18" t="str">
         <v/>
       </c>
       <c r="O18" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R18" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S18" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T18" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U18" t="str">
         <v/>
@@ -1685,23 +1680,23 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v/>
+      <c r="A19">
+        <v>18</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-30 09:33:27</v>
       </c>
       <c r="D19" t="str">
         <v>抖店-靓仔甄选台球店</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>PDD20260330093327001</v>
       </c>
       <c r="F19" t="str">
-        <v>6924926230836313576</v>
+        <v>DD20260330093327001</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1710,40 +1705,40 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>TA170</v>
+        <v>TA163</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19">
-        <v>1580</v>
+        <v>996</v>
       </c>
       <c r="N19" t="str">
         <v/>
       </c>
       <c r="O19" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R19" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S19" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T19" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U19" t="str">
         <v/>
@@ -1756,23 +1751,23 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v/>
+      <c r="A20">
+        <v>19</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-30 09:33:27</v>
       </c>
       <c r="D20" t="str">
-        <v>抖店-靓仔甄选台球店</v>
+        <v>抖店-王孟南台球教学店</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>PDD20260330093327002</v>
       </c>
       <c r="F20" t="str">
-        <v>6951346507425191308</v>
+        <v>DD20260330093327002</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1781,40 +1776,40 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>快递</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>TA170</v>
+        <v>TA013</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>1580</v>
+        <v>823</v>
       </c>
       <c r="N20" t="str">
         <v/>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>13800138000</v>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>广东省深圳市龙华区xxx</v>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>广东</v>
       </c>
       <c r="S20" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="T20" t="str">
-        <v/>
+        <v>龙华</v>
       </c>
       <c r="U20" t="str">
         <v/>
@@ -1823,109 +1818,1032 @@
         <v/>
       </c>
       <c r="W20" t="str">
-        <v>已发货</v>
+        <v>已完成</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v/>
+      <c r="A21">
+        <v>20</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>2026-03-17 00:00:00</v>
+        <v>2026-03-30 09:33:27</v>
       </c>
       <c r="D21" t="str">
+        <v>抖店-好事情台球</v>
+      </c>
+      <c r="E21" t="str">
+        <v>PDD20260330093327003</v>
+      </c>
+      <c r="F21" t="str">
+        <v>DD20260330093327003</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>TA013</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>642</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P21" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R21" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S21" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T21" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-03-30 09:33:27</v>
+      </c>
+      <c r="D22" t="str">
         <v>抖店-靓仔甄选台球店</v>
       </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v>6924913470897684347</v>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
+      <c r="E22" t="str">
+        <v>PDD20260330093327004</v>
+      </c>
+      <c r="F22" t="str">
+        <v>DD20260330093327004</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>TB001</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>631</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P22" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R22" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S22" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T22" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-03-31 09:38:33</v>
+      </c>
+      <c r="D23" t="str">
+        <v>抖店-台球four号店</v>
+      </c>
+      <c r="E23" t="str">
+        <v>PDD20260331093833000</v>
+      </c>
+      <c r="F23" t="str">
+        <v>DD20260331093833000</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>TB001</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>465</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P23" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R23" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S23" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T23" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <v>待发货</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-03-31 09:38:33</v>
+      </c>
+      <c r="D24" t="str">
+        <v>抖店-台球four号店</v>
+      </c>
+      <c r="E24" t="str">
+        <v>PDD20260331093833001</v>
+      </c>
+      <c r="F24" t="str">
+        <v>DD20260331093833001</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>DAD005</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>846</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P24" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R24" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S24" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T24" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-03-31 09:38:33</v>
+      </c>
+      <c r="D25" t="str">
+        <v>抖店-靓仔甄选台球店</v>
+      </c>
+      <c r="E25" t="str">
+        <v>PDD20260331093833002</v>
+      </c>
+      <c r="F25" t="str">
+        <v>DD20260331093833002</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>DAB002</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>912</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P25" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R25" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S25" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T25" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-03-31 09:38:33</v>
+      </c>
+      <c r="D26" t="str">
+        <v>抖店-王孟南台球教学店</v>
+      </c>
+      <c r="E26" t="str">
+        <v>PDD20260331093833003</v>
+      </c>
+      <c r="F26" t="str">
+        <v>DD20260331093833003</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
         <v>TA170</v>
       </c>
-      <c r="L21">
+      <c r="L26">
         <v>1</v>
       </c>
-      <c r="M21">
-        <v>1580</v>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21" t="str">
-        <v/>
-      </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
-      <c r="U21" t="str">
-        <v/>
-      </c>
-      <c r="V21" t="str">
-        <v/>
-      </c>
-      <c r="W21" t="str">
+      <c r="M26">
+        <v>582</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P26" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R26" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S26" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T26" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-03-31 09:38:33</v>
+      </c>
+      <c r="D27" t="str">
+        <v>抖店-王孟南台球教学店</v>
+      </c>
+      <c r="E27" t="str">
+        <v>PDD20260331093833004</v>
+      </c>
+      <c r="F27" t="str">
+        <v>DD20260331093833004</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>DAD003</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>648</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P27" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R27" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S27" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T27" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>2026-04-01 17:09:02</v>
+      </c>
+      <c r="D28" t="str">
+        <v>抖店-好事情台球</v>
+      </c>
+      <c r="E28" t="str">
+        <v>PDD20260401170902000</v>
+      </c>
+      <c r="F28" t="str">
+        <v>DD20260401170902000</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>TA175</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>321</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P28" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R28" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S28" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T28" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>2026-04-01 17:09:02</v>
+      </c>
+      <c r="D29" t="str">
+        <v>抖店-王孟南台球教学店</v>
+      </c>
+      <c r="E29" t="str">
+        <v>PDD20260401170902001</v>
+      </c>
+      <c r="F29" t="str">
+        <v>DD20260401170902001</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>DAB002</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>467</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P29" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R29" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S29" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T29" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>2026-04-01 17:09:02</v>
+      </c>
+      <c r="D30" t="str">
+        <v>抖店-台球four号店</v>
+      </c>
+      <c r="E30" t="str">
+        <v>PDD20260401170902002</v>
+      </c>
+      <c r="F30" t="str">
+        <v>DD20260401170902002</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>TA013</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="M30">
+        <v>565</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P30" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R30" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S30" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T30" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v>2026-04-01 17:09:02</v>
+      </c>
+      <c r="D31" t="str">
+        <v>抖店-好事情台球</v>
+      </c>
+      <c r="E31" t="str">
+        <v>PDD20260401170902003</v>
+      </c>
+      <c r="F31" t="str">
+        <v>DD20260401170902003</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>TA170</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>804</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P31" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R31" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S31" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T31" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U31" t="str">
+        <v/>
+      </c>
+      <c r="V31" t="str">
+        <v/>
+      </c>
+      <c r="W31" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v>2026-04-01 17:09:02</v>
+      </c>
+      <c r="D32" t="str">
+        <v>抖店-台球four号店</v>
+      </c>
+      <c r="E32" t="str">
+        <v>PDD20260401170902004</v>
+      </c>
+      <c r="F32" t="str">
+        <v>DD20260401170902004</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>DAD011</v>
+      </c>
+      <c r="L32">
+        <v>3</v>
+      </c>
+      <c r="M32">
+        <v>109</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P32" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R32" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S32" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T32" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U32" t="str">
+        <v/>
+      </c>
+      <c r="V32" t="str">
+        <v/>
+      </c>
+      <c r="W32" t="str">
+        <v>已完成</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>2026-04-01 17:09:02</v>
+      </c>
+      <c r="D33" t="str">
+        <v>抖店-台球four号店</v>
+      </c>
+      <c r="E33" t="str">
+        <v>PDD20260401170902005</v>
+      </c>
+      <c r="F33" t="str">
+        <v>DD20260401170902005</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>TB001</v>
+      </c>
+      <c r="L33">
+        <v>3</v>
+      </c>
+      <c r="M33">
+        <v>184</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P33" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R33" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S33" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T33" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U33" t="str">
+        <v/>
+      </c>
+      <c r="V33" t="str">
+        <v/>
+      </c>
+      <c r="W33" t="str">
+        <v>待发货</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>2026-04-01 17:09:02</v>
+      </c>
+      <c r="D34" t="str">
+        <v>抖店-台球four号店</v>
+      </c>
+      <c r="E34" t="str">
+        <v>PDD20260401170902006</v>
+      </c>
+      <c r="F34" t="str">
+        <v>DD20260401170902006</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>快递</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>DAD011</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>285</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v>张三</v>
+      </c>
+      <c r="P34" t="str">
+        <v>13800138000</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>广东省深圳市龙华区xxx</v>
+      </c>
+      <c r="R34" t="str">
+        <v>广东</v>
+      </c>
+      <c r="S34" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="T34" t="str">
+        <v>龙华</v>
+      </c>
+      <c r="U34" t="str">
+        <v/>
+      </c>
+      <c r="V34" t="str">
+        <v/>
+      </c>
+      <c r="W34" t="str">
         <v>已完成</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AH29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v/>
+        <v>序号</v>
       </c>
       <c r="B1" t="str">
         <v/>
       </c>
       <c r="C1" t="str">
-        <v/>
+        <v>订单时间</v>
       </c>
       <c r="D1" t="str">
         <v>店铺</v>
       </c>
       <c r="E1" t="str">
-        <v>订单号</v>
+        <v>订单编号</v>
       </c>
       <c r="F1" t="str">
-        <v/>
+        <v>商品名称</v>
       </c>
       <c r="G1" t="str">
         <v/>
@@ -1934,16 +2852,16 @@
         <v/>
       </c>
       <c r="I1" t="str">
-        <v/>
+        <v>订单状态</v>
       </c>
       <c r="J1" t="str">
-        <v/>
+        <v>订单状态2</v>
       </c>
       <c r="K1" t="str">
-        <v>订单状态</v>
+        <v>实付款</v>
       </c>
       <c r="L1" t="str">
-        <v>实付款</v>
+        <v/>
       </c>
       <c r="M1" t="str">
         <v/>
@@ -2006,24 +2924,27 @@
         <v/>
       </c>
       <c r="AG1" t="str">
+        <v/>
+      </c>
+      <c r="AH1" t="str">
         <v>SKU编码</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
+      <c r="A2">
+        <v>34</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>2026-03-26 14:26:03</v>
       </c>
       <c r="D2" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E2" t="str">
-        <v>2608600081628652</v>
+        <v>KS20260326142603000</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -2035,16 +2956,16 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L2">
-        <v>1980</v>
+        <v>311</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -2107,24 +3028,24 @@
         <v/>
       </c>
       <c r="AG2" t="str">
-        <v>TA013</v>
+        <v>DAD005</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v/>
+      <c r="A3">
+        <v>35</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>2026-03-26 00:00:00</v>
+        <v>2026-03-26 14:26:03</v>
       </c>
       <c r="D3" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E3" t="str">
-        <v>2608502022315420</v>
+        <v>KS20260326142603001</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -2136,16 +3057,16 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>2026-03-26 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L3">
-        <v>1980</v>
+        <v>410</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -2208,24 +3129,24 @@
         <v/>
       </c>
       <c r="AG3" t="str">
-        <v>TA013</v>
+        <v>DAB002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v/>
+      <c r="A4">
+        <v>36</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>2026-03-26 00:00:00</v>
+        <v>2026-03-26 14:26:03</v>
       </c>
       <c r="D4" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E4" t="str">
-        <v>2608500584781131</v>
+        <v>KS20260326142603002</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -2237,16 +3158,16 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>2026-03-26 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L4">
-        <v>1280</v>
+        <v>434</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -2309,24 +3230,24 @@
         <v/>
       </c>
       <c r="AG4" t="str">
-        <v>TA163</v>
+        <v>TA175</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v/>
+      <c r="A5">
+        <v>37</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>2026-03-26 14:26:03</v>
       </c>
       <c r="D5" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E5" t="str">
-        <v>2608600481669183</v>
+        <v>KS20260326142603003</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -2338,16 +3259,16 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L5">
-        <v>1280</v>
+        <v>382</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -2414,20 +3335,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v/>
+      <c r="A6">
+        <v>38</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>2026-03-26 14:26:03</v>
       </c>
       <c r="D6" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E6" t="str">
-        <v>2608601680874956</v>
+        <v>KS20260326142603004</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -2439,16 +3360,16 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L6">
-        <v>990</v>
+        <v>597</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -2511,24 +3432,24 @@
         <v/>
       </c>
       <c r="AG6" t="str">
-        <v>TA175</v>
+        <v>TA170</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v/>
+      <c r="A7">
+        <v>39</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>2026-03-27 18:43:21</v>
       </c>
       <c r="D7" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E7" t="str">
-        <v>2608600483252167</v>
+        <v>KS20260327184321000</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -2540,16 +3461,16 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L7">
-        <v>990</v>
+        <v>183</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -2612,24 +3533,24 @@
         <v/>
       </c>
       <c r="AG7" t="str">
-        <v>TA175</v>
+        <v>DAB002</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v/>
+      <c r="A8">
+        <v>40</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>2026-03-27 18:43:21</v>
       </c>
       <c r="D8" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E8" t="str">
-        <v>2608602002474773</v>
+        <v>KS20260327184321001</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -2641,16 +3562,16 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L8">
-        <v>1980</v>
+        <v>327</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -2713,24 +3634,24 @@
         <v/>
       </c>
       <c r="AG8" t="str">
-        <v>TA013</v>
+        <v>TA175</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v/>
+      <c r="A9">
+        <v>41</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>2026-03-27 18:43:21</v>
       </c>
       <c r="D9" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E9" t="str">
-        <v>2608600321644119</v>
+        <v>KS20260327184321002</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -2742,16 +3663,16 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L9">
-        <v>990</v>
+        <v>515</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -2814,24 +3735,24 @@
         <v/>
       </c>
       <c r="AG9" t="str">
-        <v>TA175</v>
+        <v>DAD003</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v/>
+      <c r="A10">
+        <v>42</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>2026-03-27 18:43:21</v>
       </c>
       <c r="D10" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E10" t="str">
-        <v>2608602080817420</v>
+        <v>KS20260327184321003</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -2843,16 +3764,16 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>2026-03-27 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L10">
-        <v>990</v>
+        <v>102</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -2915,24 +3836,24 @@
         <v/>
       </c>
       <c r="AG10" t="str">
-        <v>TA175</v>
+        <v>TA163</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v/>
+      <c r="A11">
+        <v>43</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>2026-03-26 00:00:00</v>
+        <v>2026-03-28 17:22:31</v>
       </c>
       <c r="D11" t="str">
         <v>快手-王孟南台球教学</v>
       </c>
       <c r="E11" t="str">
-        <v>2608500349356498</v>
+        <v>KS20260328172231000</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -2944,16 +3865,16 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>2026-03-26 00:00:00</v>
+        <v>交易成功</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>已发货</v>
+        <v>交易成功</v>
       </c>
       <c r="L11">
-        <v>990</v>
+        <v>488</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -3016,23 +3937,1841 @@
         <v/>
       </c>
       <c r="AG11" t="str">
+        <v>TA163</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>44</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-03-28 17:22:31</v>
+      </c>
+      <c r="D12" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E12" t="str">
+        <v>KS20260328172231001</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L12">
+        <v>276</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
+        <v/>
+      </c>
+      <c r="AD12" t="str">
+        <v/>
+      </c>
+      <c r="AE12" t="str">
+        <v/>
+      </c>
+      <c r="AF12" t="str">
+        <v/>
+      </c>
+      <c r="AG12" t="str">
+        <v>TA163</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>45</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-03-29 19:33:45</v>
+      </c>
+      <c r="D13" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E13" t="str">
+        <v>KS20260329193345000</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L13">
+        <v>567</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
+        <v/>
+      </c>
+      <c r="AD13" t="str">
+        <v/>
+      </c>
+      <c r="AE13" t="str">
+        <v/>
+      </c>
+      <c r="AF13" t="str">
+        <v/>
+      </c>
+      <c r="AG13" t="str">
+        <v>TB001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>46</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-03-29 19:33:45</v>
+      </c>
+      <c r="D14" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E14" t="str">
+        <v>KS20260329193345001</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L14">
+        <v>380</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
+        <v/>
+      </c>
+      <c r="AE14" t="str">
+        <v/>
+      </c>
+      <c r="AF14" t="str">
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <v>DAD005</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>47</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-03-29 19:33:45</v>
+      </c>
+      <c r="D15" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E15" t="str">
+        <v>KS20260329193345002</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L15">
+        <v>663</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <v>TA013</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>48</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-03-29 19:33:45</v>
+      </c>
+      <c r="D16" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E16" t="str">
+        <v>KS20260329193345003</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L16">
+        <v>376</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+      <c r="AD16" t="str">
+        <v/>
+      </c>
+      <c r="AE16" t="str">
+        <v/>
+      </c>
+      <c r="AF16" t="str">
+        <v/>
+      </c>
+      <c r="AG16" t="str">
+        <v>DAA074</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>49</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-03-30 10:55:10</v>
+      </c>
+      <c r="D17" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E17" t="str">
+        <v>KS20260330105510000</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L17">
+        <v>256</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
+        <v/>
+      </c>
+      <c r="AD17" t="str">
+        <v/>
+      </c>
+      <c r="AE17" t="str">
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <v>DAD003</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>50</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-03-30 10:55:10</v>
+      </c>
+      <c r="D18" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E18" t="str">
+        <v>KS20260330105510001</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L18">
+        <v>228</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
+        <v/>
+      </c>
+      <c r="AA18" t="str">
+        <v/>
+      </c>
+      <c r="AB18" t="str">
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <v/>
+      </c>
+      <c r="AD18" t="str">
+        <v/>
+      </c>
+      <c r="AE18" t="str">
+        <v/>
+      </c>
+      <c r="AF18" t="str">
+        <v/>
+      </c>
+      <c r="AG18" t="str">
+        <v>TA170</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>51</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-03-30 10:55:10</v>
+      </c>
+      <c r="D19" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E19" t="str">
+        <v>KS20260330105510002</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L19">
+        <v>556</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19" t="str">
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
+        <v/>
+      </c>
+      <c r="AA19" t="str">
+        <v/>
+      </c>
+      <c r="AB19" t="str">
+        <v/>
+      </c>
+      <c r="AC19" t="str">
+        <v/>
+      </c>
+      <c r="AD19" t="str">
+        <v/>
+      </c>
+      <c r="AE19" t="str">
+        <v/>
+      </c>
+      <c r="AF19" t="str">
+        <v/>
+      </c>
+      <c r="AG19" t="str">
+        <v>DAD003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>52</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-03-30 10:55:10</v>
+      </c>
+      <c r="D20" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E20" t="str">
+        <v>KS20260330105510003</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L20">
+        <v>232</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20" t="str">
+        <v/>
+      </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="str">
+        <v/>
+      </c>
+      <c r="AA20" t="str">
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <v/>
+      </c>
+      <c r="AE20" t="str">
+        <v/>
+      </c>
+      <c r="AF20" t="str">
+        <v/>
+      </c>
+      <c r="AG20" t="str">
+        <v>TB001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>53</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-03-30 10:55:10</v>
+      </c>
+      <c r="D21" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E21" t="str">
+        <v>KS20260330105510004</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L21">
+        <v>643</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
+        <v/>
+      </c>
+      <c r="AA21" t="str">
+        <v/>
+      </c>
+      <c r="AB21" t="str">
+        <v/>
+      </c>
+      <c r="AC21" t="str">
+        <v/>
+      </c>
+      <c r="AD21" t="str">
+        <v/>
+      </c>
+      <c r="AE21" t="str">
+        <v/>
+      </c>
+      <c r="AF21" t="str">
+        <v/>
+      </c>
+      <c r="AG21" t="str">
         <v>TA175</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>54</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-03-31 11:04:00</v>
+      </c>
+      <c r="D22" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E22" t="str">
+        <v>KS20260331110400000</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L22">
+        <v>669</v>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="str">
+        <v/>
+      </c>
+      <c r="AA22" t="str">
+        <v/>
+      </c>
+      <c r="AB22" t="str">
+        <v/>
+      </c>
+      <c r="AC22" t="str">
+        <v/>
+      </c>
+      <c r="AD22" t="str">
+        <v/>
+      </c>
+      <c r="AE22" t="str">
+        <v/>
+      </c>
+      <c r="AF22" t="str">
+        <v/>
+      </c>
+      <c r="AG22" t="str">
+        <v>TA175</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>55</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-03-31 11:04:00</v>
+      </c>
+      <c r="D23" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E23" t="str">
+        <v>KS20260331110400001</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L23">
+        <v>145</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
+        <v/>
+      </c>
+      <c r="AA23" t="str">
+        <v/>
+      </c>
+      <c r="AB23" t="str">
+        <v/>
+      </c>
+      <c r="AC23" t="str">
+        <v/>
+      </c>
+      <c r="AD23" t="str">
+        <v/>
+      </c>
+      <c r="AE23" t="str">
+        <v/>
+      </c>
+      <c r="AF23" t="str">
+        <v/>
+      </c>
+      <c r="AG23" t="str">
+        <v>DAB002</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>56</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-03-31 11:04:00</v>
+      </c>
+      <c r="D24" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E24" t="str">
+        <v>KS20260331110400002</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L24">
+        <v>488</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+      <c r="Z24" t="str">
+        <v/>
+      </c>
+      <c r="AA24" t="str">
+        <v/>
+      </c>
+      <c r="AB24" t="str">
+        <v/>
+      </c>
+      <c r="AC24" t="str">
+        <v/>
+      </c>
+      <c r="AD24" t="str">
+        <v/>
+      </c>
+      <c r="AE24" t="str">
+        <v/>
+      </c>
+      <c r="AF24" t="str">
+        <v/>
+      </c>
+      <c r="AG24" t="str">
+        <v>TA013</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>57</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-03-31 11:04:00</v>
+      </c>
+      <c r="D25" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E25" t="str">
+        <v>KS20260331110400003</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L25">
+        <v>165</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <v/>
+      </c>
+      <c r="Z25" t="str">
+        <v/>
+      </c>
+      <c r="AA25" t="str">
+        <v/>
+      </c>
+      <c r="AB25" t="str">
+        <v/>
+      </c>
+      <c r="AC25" t="str">
+        <v/>
+      </c>
+      <c r="AD25" t="str">
+        <v/>
+      </c>
+      <c r="AE25" t="str">
+        <v/>
+      </c>
+      <c r="AF25" t="str">
+        <v/>
+      </c>
+      <c r="AG25" t="str">
+        <v>TA175</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>58</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-04-01 10:17:08</v>
+      </c>
+      <c r="D26" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E26" t="str">
+        <v>KS20260401101708000</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L26">
+        <v>564</v>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
+      </c>
+      <c r="Z26" t="str">
+        <v/>
+      </c>
+      <c r="AA26" t="str">
+        <v/>
+      </c>
+      <c r="AB26" t="str">
+        <v/>
+      </c>
+      <c r="AC26" t="str">
+        <v/>
+      </c>
+      <c r="AD26" t="str">
+        <v/>
+      </c>
+      <c r="AE26" t="str">
+        <v/>
+      </c>
+      <c r="AF26" t="str">
+        <v/>
+      </c>
+      <c r="AG26" t="str">
+        <v>TA013</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>59</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-04-01 10:17:08</v>
+      </c>
+      <c r="D27" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E27" t="str">
+        <v>KS20260401101708001</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L27">
+        <v>246</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
+        <v/>
+      </c>
+      <c r="Z27" t="str">
+        <v/>
+      </c>
+      <c r="AA27" t="str">
+        <v/>
+      </c>
+      <c r="AB27" t="str">
+        <v/>
+      </c>
+      <c r="AC27" t="str">
+        <v/>
+      </c>
+      <c r="AD27" t="str">
+        <v/>
+      </c>
+      <c r="AE27" t="str">
+        <v/>
+      </c>
+      <c r="AF27" t="str">
+        <v/>
+      </c>
+      <c r="AG27" t="str">
+        <v>TA175</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>60</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>2026-04-01 10:17:08</v>
+      </c>
+      <c r="D28" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E28" t="str">
+        <v>KS20260401101708002</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L28">
+        <v>440</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
+        <v/>
+      </c>
+      <c r="Z28" t="str">
+        <v/>
+      </c>
+      <c r="AA28" t="str">
+        <v/>
+      </c>
+      <c r="AB28" t="str">
+        <v/>
+      </c>
+      <c r="AC28" t="str">
+        <v/>
+      </c>
+      <c r="AD28" t="str">
+        <v/>
+      </c>
+      <c r="AE28" t="str">
+        <v/>
+      </c>
+      <c r="AF28" t="str">
+        <v/>
+      </c>
+      <c r="AG28" t="str">
+        <v>DAA074</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>61</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>2026-04-01 10:17:08</v>
+      </c>
+      <c r="D29" t="str">
+        <v>快手-王孟南台球教学</v>
+      </c>
+      <c r="E29" t="str">
+        <v>KS20260401101708003</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>交易成功</v>
+      </c>
+      <c r="L29">
+        <v>627</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <v/>
+      </c>
+      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
+        <v/>
+      </c>
+      <c r="Z29" t="str">
+        <v/>
+      </c>
+      <c r="AA29" t="str">
+        <v/>
+      </c>
+      <c r="AB29" t="str">
+        <v/>
+      </c>
+      <c r="AC29" t="str">
+        <v/>
+      </c>
+      <c r="AD29" t="str">
+        <v/>
+      </c>
+      <c r="AE29" t="str">
+        <v/>
+      </c>
+      <c r="AF29" t="str">
+        <v/>
+      </c>
+      <c r="AG29" t="str">
+        <v>TA013</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AG11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AH29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AV11"/>
+  <dimension ref="A1:AW25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v/>
+        <v>序号</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -3047,7 +5786,7 @@
         <v>订单号</v>
       </c>
       <c r="F1" t="str">
-        <v>订单下单时间</v>
+        <v>下单时间</v>
       </c>
       <c r="G1" t="str">
         <v/>
@@ -3056,10 +5795,10 @@
         <v/>
       </c>
       <c r="I1" t="str">
-        <v/>
+        <v>订单状态</v>
       </c>
       <c r="J1" t="str">
-        <v>订单状态</v>
+        <v/>
       </c>
       <c r="K1" t="str">
         <v/>
@@ -3095,105 +5834,102 @@
         <v/>
       </c>
       <c r="V1" t="str">
+        <v/>
+      </c>
+      <c r="W1" t="str">
+        <v/>
+      </c>
+      <c r="X1" t="str">
+        <v/>
+      </c>
+      <c r="Y1" t="str">
+        <v/>
+      </c>
+      <c r="Z1" t="str">
+        <v/>
+      </c>
+      <c r="AA1" t="str">
+        <v/>
+      </c>
+      <c r="AB1" t="str">
+        <v/>
+      </c>
+      <c r="AC1" t="str">
+        <v/>
+      </c>
+      <c r="AD1" t="str">
+        <v/>
+      </c>
+      <c r="AE1" t="str">
+        <v/>
+      </c>
+      <c r="AF1" t="str">
+        <v/>
+      </c>
+      <c r="AG1" t="str">
+        <v/>
+      </c>
+      <c r="AH1" t="str">
+        <v/>
+      </c>
+      <c r="AI1" t="str">
+        <v/>
+      </c>
+      <c r="AJ1" t="str">
+        <v/>
+      </c>
+      <c r="AK1" t="str">
+        <v/>
+      </c>
+      <c r="AL1" t="str">
+        <v/>
+      </c>
+      <c r="AM1" t="str">
+        <v/>
+      </c>
+      <c r="AN1" t="str">
+        <v/>
+      </c>
+      <c r="AO1" t="str">
+        <v/>
+      </c>
+      <c r="AP1" t="str">
+        <v/>
+      </c>
+      <c r="AQ1" t="str">
+        <v/>
+      </c>
+      <c r="AR1" t="str">
+        <v/>
+      </c>
+      <c r="AS1" t="str">
+        <v/>
+      </c>
+      <c r="AT1" t="str">
+        <v>SKU编码</v>
+      </c>
+      <c r="AU1" t="str">
         <v>订单实际支付金额</v>
-      </c>
-      <c r="W1" t="str">
-        <v/>
-      </c>
-      <c r="X1" t="str">
-        <v/>
-      </c>
-      <c r="Y1" t="str">
-        <v/>
-      </c>
-      <c r="Z1" t="str">
-        <v/>
-      </c>
-      <c r="AA1" t="str">
-        <v/>
-      </c>
-      <c r="AB1" t="str">
-        <v/>
-      </c>
-      <c r="AC1" t="str">
-        <v/>
-      </c>
-      <c r="AD1" t="str">
-        <v/>
-      </c>
-      <c r="AE1" t="str">
-        <v/>
-      </c>
-      <c r="AF1" t="str">
-        <v/>
-      </c>
-      <c r="AG1" t="str">
-        <v/>
-      </c>
-      <c r="AH1" t="str">
-        <v/>
-      </c>
-      <c r="AI1" t="str">
-        <v/>
-      </c>
-      <c r="AJ1" t="str">
-        <v/>
-      </c>
-      <c r="AK1" t="str">
-        <v/>
-      </c>
-      <c r="AL1" t="str">
-        <v/>
-      </c>
-      <c r="AM1" t="str">
-        <v/>
-      </c>
-      <c r="AN1" t="str">
-        <v/>
-      </c>
-      <c r="AO1" t="str">
-        <v/>
-      </c>
-      <c r="AP1" t="str">
-        <v/>
-      </c>
-      <c r="AQ1" t="str">
-        <v/>
-      </c>
-      <c r="AR1" t="str">
-        <v/>
-      </c>
-      <c r="AS1" t="str">
-        <v/>
-      </c>
-      <c r="AT1" t="str">
-        <v/>
-      </c>
-      <c r="AU1" t="str">
-        <v/>
-      </c>
-      <c r="AV1" t="str">
-        <v>SKU编码(自定义)</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
+      <c r="A2">
+        <v>62</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>2026-03-27 01:25:53</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>视频号-靓仔台球</v>
       </c>
       <c r="E2" t="str">
-        <v>3735273014859804928</v>
+        <v>SPH20260326101020000</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-03-27 01:25:53</v>
+        <v>2026-03-26 10:10:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -3205,7 +5941,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -3241,7 +5977,7 @@
         <v/>
       </c>
       <c r="V2">
-        <v>990</v>
+        <v>667</v>
       </c>
       <c r="W2" t="str">
         <v/>
@@ -3319,27 +6055,30 @@
         <v/>
       </c>
       <c r="AV2" t="str">
-        <v>TA175</v>
+        <v>DAD005</v>
+      </c>
+      <c r="AW2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v/>
+      <c r="A3">
+        <v>63</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>2026-03-27 00:31:07</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>视频号-靓仔台球</v>
       </c>
       <c r="E3" t="str">
-        <v>3735272153652550144</v>
+        <v>SPH20260326101020001</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-03-27 00:31:07</v>
+        <v>2026-03-26 10:10:20</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -3351,7 +6090,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -3387,7 +6126,7 @@
         <v/>
       </c>
       <c r="V3">
-        <v>990</v>
+        <v>635</v>
       </c>
       <c r="W3" t="str">
         <v/>
@@ -3467,25 +6206,28 @@
       <c r="AV3" t="str">
         <v>TA175</v>
       </c>
+      <c r="AW3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v/>
+      <c r="A4">
+        <v>64</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>2026-03-27 00:19:39</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>视频号-靓仔台球</v>
+        <v>视频号-王孟南台球教学</v>
       </c>
       <c r="E4" t="str">
-        <v>3735271972019524096</v>
+        <v>SPH20260326101020002</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-03-27 00:19:39</v>
+        <v>2026-03-26 10:10:20</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -3497,7 +6239,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -3533,7 +6275,7 @@
         <v/>
       </c>
       <c r="V4">
-        <v>1980</v>
+        <v>676</v>
       </c>
       <c r="W4" t="str">
         <v/>
@@ -3611,27 +6353,30 @@
         <v/>
       </c>
       <c r="AV4" t="str">
-        <v>TA013</v>
+        <v>TA170</v>
+      </c>
+      <c r="AW4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v/>
+      <c r="A5">
+        <v>65</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>2026-03-27 00:19:05</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v>视频号-靓仔台球</v>
       </c>
       <c r="E5" t="str">
-        <v>3735271963749147648</v>
+        <v>SPH20260327101905000</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-03-27 00:19:05</v>
+        <v>2026-03-27 10:19:05</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -3643,7 +6388,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -3679,7 +6424,7 @@
         <v/>
       </c>
       <c r="V5">
-        <v>1980</v>
+        <v>808</v>
       </c>
       <c r="W5" t="str">
         <v/>
@@ -3757,27 +6502,30 @@
         <v/>
       </c>
       <c r="AV5" t="str">
-        <v>TA013</v>
+        <v>TA170</v>
+      </c>
+      <c r="AW5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v/>
+      <c r="A6">
+        <v>66</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>2026-03-27 00:18:05</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v>视频号-靓仔台球</v>
       </c>
       <c r="E6" t="str">
-        <v>3735271947611035136</v>
+        <v>SPH20260327101905001</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-03-27 00:18:05</v>
+        <v>2026-03-27 10:19:05</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -3789,7 +6537,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -3825,7 +6573,7 @@
         <v/>
       </c>
       <c r="V6">
-        <v>1980</v>
+        <v>106</v>
       </c>
       <c r="W6" t="str">
         <v/>
@@ -3903,27 +6651,30 @@
         <v/>
       </c>
       <c r="AV6" t="str">
-        <v>TA013</v>
+        <v>DAD011</v>
+      </c>
+      <c r="AW6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v/>
+      <c r="A7">
+        <v>67</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>2026-03-26 23:37:11</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>视频号-靓仔台球</v>
+        <v>视频号-王孟南台球教学</v>
       </c>
       <c r="E7" t="str">
-        <v>3735271305478556928</v>
+        <v>SPH20260327101905002</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-03-26 23:37:11</v>
+        <v>2026-03-27 10:19:05</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -3935,7 +6686,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -3971,7 +6722,7 @@
         <v/>
       </c>
       <c r="V7">
-        <v>1980</v>
+        <v>615</v>
       </c>
       <c r="W7" t="str">
         <v/>
@@ -4049,27 +6800,30 @@
         <v/>
       </c>
       <c r="AV7" t="str">
-        <v>TA013</v>
+        <v>TA175</v>
+      </c>
+      <c r="AW7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v/>
+      <c r="A8">
+        <v>68</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>2026-03-26 23:21:53</v>
+        <v/>
       </c>
       <c r="D8" t="str">
         <v>视频号-靓仔台球</v>
       </c>
       <c r="E8" t="str">
-        <v>3735271062864282624</v>
+        <v>SPH20260328112402000</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-03-26 23:21:53</v>
+        <v>2026-03-28 11:24:02</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -4081,7 +6835,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -4117,7 +6871,7 @@
         <v/>
       </c>
       <c r="V8">
-        <v>1280</v>
+        <v>410</v>
       </c>
       <c r="W8" t="str">
         <v/>
@@ -4195,27 +6949,30 @@
         <v/>
       </c>
       <c r="AV8" t="str">
-        <v>TA163</v>
+        <v>DAB002</v>
+      </c>
+      <c r="AW8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v/>
+      <c r="A9">
+        <v>69</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>2026-03-26 22:41:09</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>视频号-靓仔台球</v>
+        <v>视频号-王孟南台球教学</v>
       </c>
       <c r="E9" t="str">
-        <v>3735270419829512960</v>
+        <v>SPH20260328112402001</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-03-26 22:41:09</v>
+        <v>2026-03-28 11:24:02</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -4227,7 +6984,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -4263,7 +7020,7 @@
         <v/>
       </c>
       <c r="V9">
-        <v>990</v>
+        <v>402</v>
       </c>
       <c r="W9" t="str">
         <v/>
@@ -4341,27 +7098,30 @@
         <v/>
       </c>
       <c r="AV9" t="str">
-        <v>TA175</v>
+        <v>DAB002</v>
+      </c>
+      <c r="AW9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v/>
+      <c r="A10">
+        <v>70</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>2026-03-26 22:40:49</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>视频号-靓仔台球</v>
+        <v>视频号-王孟南台球教学</v>
       </c>
       <c r="E10" t="str">
-        <v>3735270404497232384</v>
+        <v>SPH20260328112402002</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-03-26 22:40:49</v>
+        <v>2026-03-28 11:24:02</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -4373,7 +7133,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -4409,7 +7169,7 @@
         <v/>
       </c>
       <c r="V10">
-        <v>990</v>
+        <v>279</v>
       </c>
       <c r="W10" t="str">
         <v/>
@@ -4487,27 +7247,30 @@
         <v/>
       </c>
       <c r="AV10" t="str">
-        <v>TA175</v>
+        <v>DAD003</v>
+      </c>
+      <c r="AW10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v/>
+      <c r="A11">
+        <v>71</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>2026-03-26 22:26:43</v>
+        <v/>
       </c>
       <c r="D11" t="str">
         <v>视频号-靓仔台球</v>
       </c>
       <c r="E11" t="str">
-        <v>3735270197125075456</v>
+        <v>SPH20260329120227000</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-03-26 22:26:43</v>
+        <v>2026-03-29 12:02:27</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -4519,7 +7282,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>已发货</v>
+        <v>待发货</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -4555,7 +7318,7 @@
         <v/>
       </c>
       <c r="V11">
-        <v>1980</v>
+        <v>718</v>
       </c>
       <c r="W11" t="str">
         <v/>
@@ -4634,563 +7397,2100 @@
       </c>
       <c r="AV11" t="str">
         <v>TA013</v>
+      </c>
+      <c r="AW11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>72</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E12" t="str">
+        <v>SPH20260329120227001</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-03-29 12:02:27</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12">
+        <v>742</v>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
+        <v/>
+      </c>
+      <c r="AD12" t="str">
+        <v/>
+      </c>
+      <c r="AE12" t="str">
+        <v/>
+      </c>
+      <c r="AF12" t="str">
+        <v/>
+      </c>
+      <c r="AG12" t="str">
+        <v/>
+      </c>
+      <c r="AH12" t="str">
+        <v/>
+      </c>
+      <c r="AI12" t="str">
+        <v/>
+      </c>
+      <c r="AJ12" t="str">
+        <v/>
+      </c>
+      <c r="AK12" t="str">
+        <v/>
+      </c>
+      <c r="AL12" t="str">
+        <v/>
+      </c>
+      <c r="AM12" t="str">
+        <v/>
+      </c>
+      <c r="AN12" t="str">
+        <v/>
+      </c>
+      <c r="AO12" t="str">
+        <v/>
+      </c>
+      <c r="AP12" t="str">
+        <v/>
+      </c>
+      <c r="AQ12" t="str">
+        <v/>
+      </c>
+      <c r="AR12" t="str">
+        <v/>
+      </c>
+      <c r="AS12" t="str">
+        <v/>
+      </c>
+      <c r="AT12" t="str">
+        <v/>
+      </c>
+      <c r="AU12" t="str">
+        <v/>
+      </c>
+      <c r="AV12" t="str">
+        <v>TB001</v>
+      </c>
+      <c r="AW12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>73</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>视频号-靓仔台球</v>
+      </c>
+      <c r="E13" t="str">
+        <v>SPH20260329120227002</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-03-29 12:02:27</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13">
+        <v>241</v>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
+        <v/>
+      </c>
+      <c r="AD13" t="str">
+        <v/>
+      </c>
+      <c r="AE13" t="str">
+        <v/>
+      </c>
+      <c r="AF13" t="str">
+        <v/>
+      </c>
+      <c r="AG13" t="str">
+        <v/>
+      </c>
+      <c r="AH13" t="str">
+        <v/>
+      </c>
+      <c r="AI13" t="str">
+        <v/>
+      </c>
+      <c r="AJ13" t="str">
+        <v/>
+      </c>
+      <c r="AK13" t="str">
+        <v/>
+      </c>
+      <c r="AL13" t="str">
+        <v/>
+      </c>
+      <c r="AM13" t="str">
+        <v/>
+      </c>
+      <c r="AN13" t="str">
+        <v/>
+      </c>
+      <c r="AO13" t="str">
+        <v/>
+      </c>
+      <c r="AP13" t="str">
+        <v/>
+      </c>
+      <c r="AQ13" t="str">
+        <v/>
+      </c>
+      <c r="AR13" t="str">
+        <v/>
+      </c>
+      <c r="AS13" t="str">
+        <v/>
+      </c>
+      <c r="AT13" t="str">
+        <v/>
+      </c>
+      <c r="AU13" t="str">
+        <v/>
+      </c>
+      <c r="AV13" t="str">
+        <v>TB001</v>
+      </c>
+      <c r="AW13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>74</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E14" t="str">
+        <v>SPH20260330111213000</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-03-30 11:12:13</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14">
+        <v>424</v>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
+        <v/>
+      </c>
+      <c r="AE14" t="str">
+        <v/>
+      </c>
+      <c r="AF14" t="str">
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <v/>
+      </c>
+      <c r="AI14" t="str">
+        <v/>
+      </c>
+      <c r="AJ14" t="str">
+        <v/>
+      </c>
+      <c r="AK14" t="str">
+        <v/>
+      </c>
+      <c r="AL14" t="str">
+        <v/>
+      </c>
+      <c r="AM14" t="str">
+        <v/>
+      </c>
+      <c r="AN14" t="str">
+        <v/>
+      </c>
+      <c r="AO14" t="str">
+        <v/>
+      </c>
+      <c r="AP14" t="str">
+        <v/>
+      </c>
+      <c r="AQ14" t="str">
+        <v/>
+      </c>
+      <c r="AR14" t="str">
+        <v/>
+      </c>
+      <c r="AS14" t="str">
+        <v/>
+      </c>
+      <c r="AT14" t="str">
+        <v/>
+      </c>
+      <c r="AU14" t="str">
+        <v/>
+      </c>
+      <c r="AV14" t="str">
+        <v>TA013</v>
+      </c>
+      <c r="AW14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>75</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E15" t="str">
+        <v>SPH20260330111213001</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-03-30 11:12:13</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15">
+        <v>504</v>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <v/>
+      </c>
+      <c r="AH15" t="str">
+        <v/>
+      </c>
+      <c r="AI15" t="str">
+        <v/>
+      </c>
+      <c r="AJ15" t="str">
+        <v/>
+      </c>
+      <c r="AK15" t="str">
+        <v/>
+      </c>
+      <c r="AL15" t="str">
+        <v/>
+      </c>
+      <c r="AM15" t="str">
+        <v/>
+      </c>
+      <c r="AN15" t="str">
+        <v/>
+      </c>
+      <c r="AO15" t="str">
+        <v/>
+      </c>
+      <c r="AP15" t="str">
+        <v/>
+      </c>
+      <c r="AQ15" t="str">
+        <v/>
+      </c>
+      <c r="AR15" t="str">
+        <v/>
+      </c>
+      <c r="AS15" t="str">
+        <v/>
+      </c>
+      <c r="AT15" t="str">
+        <v/>
+      </c>
+      <c r="AU15" t="str">
+        <v/>
+      </c>
+      <c r="AV15" t="str">
+        <v>DAD005</v>
+      </c>
+      <c r="AW15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>76</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>视频号-靓仔台球</v>
+      </c>
+      <c r="E16" t="str">
+        <v>SPH20260330111213002</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-03-30 11:12:13</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16">
+        <v>54</v>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+      <c r="AD16" t="str">
+        <v/>
+      </c>
+      <c r="AE16" t="str">
+        <v/>
+      </c>
+      <c r="AF16" t="str">
+        <v/>
+      </c>
+      <c r="AG16" t="str">
+        <v/>
+      </c>
+      <c r="AH16" t="str">
+        <v/>
+      </c>
+      <c r="AI16" t="str">
+        <v/>
+      </c>
+      <c r="AJ16" t="str">
+        <v/>
+      </c>
+      <c r="AK16" t="str">
+        <v/>
+      </c>
+      <c r="AL16" t="str">
+        <v/>
+      </c>
+      <c r="AM16" t="str">
+        <v/>
+      </c>
+      <c r="AN16" t="str">
+        <v/>
+      </c>
+      <c r="AO16" t="str">
+        <v/>
+      </c>
+      <c r="AP16" t="str">
+        <v/>
+      </c>
+      <c r="AQ16" t="str">
+        <v/>
+      </c>
+      <c r="AR16" t="str">
+        <v/>
+      </c>
+      <c r="AS16" t="str">
+        <v/>
+      </c>
+      <c r="AT16" t="str">
+        <v/>
+      </c>
+      <c r="AU16" t="str">
+        <v/>
+      </c>
+      <c r="AV16" t="str">
+        <v>DAD003</v>
+      </c>
+      <c r="AW16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>77</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E17" t="str">
+        <v>SPH20260330111213003</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-03-30 11:12:13</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17">
+        <v>404</v>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
+        <v/>
+      </c>
+      <c r="AD17" t="str">
+        <v/>
+      </c>
+      <c r="AE17" t="str">
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <v/>
+      </c>
+      <c r="AI17" t="str">
+        <v/>
+      </c>
+      <c r="AJ17" t="str">
+        <v/>
+      </c>
+      <c r="AK17" t="str">
+        <v/>
+      </c>
+      <c r="AL17" t="str">
+        <v/>
+      </c>
+      <c r="AM17" t="str">
+        <v/>
+      </c>
+      <c r="AN17" t="str">
+        <v/>
+      </c>
+      <c r="AO17" t="str">
+        <v/>
+      </c>
+      <c r="AP17" t="str">
+        <v/>
+      </c>
+      <c r="AQ17" t="str">
+        <v/>
+      </c>
+      <c r="AR17" t="str">
+        <v/>
+      </c>
+      <c r="AS17" t="str">
+        <v/>
+      </c>
+      <c r="AT17" t="str">
+        <v/>
+      </c>
+      <c r="AU17" t="str">
+        <v/>
+      </c>
+      <c r="AV17" t="str">
+        <v>DAD005</v>
+      </c>
+      <c r="AW17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>78</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>视频号-靓仔台球</v>
+      </c>
+      <c r="E18" t="str">
+        <v>SPH20260330111213004</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-03-30 11:12:13</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18">
+        <v>150</v>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
+        <v/>
+      </c>
+      <c r="AA18" t="str">
+        <v/>
+      </c>
+      <c r="AB18" t="str">
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <v/>
+      </c>
+      <c r="AD18" t="str">
+        <v/>
+      </c>
+      <c r="AE18" t="str">
+        <v/>
+      </c>
+      <c r="AF18" t="str">
+        <v/>
+      </c>
+      <c r="AG18" t="str">
+        <v/>
+      </c>
+      <c r="AH18" t="str">
+        <v/>
+      </c>
+      <c r="AI18" t="str">
+        <v/>
+      </c>
+      <c r="AJ18" t="str">
+        <v/>
+      </c>
+      <c r="AK18" t="str">
+        <v/>
+      </c>
+      <c r="AL18" t="str">
+        <v/>
+      </c>
+      <c r="AM18" t="str">
+        <v/>
+      </c>
+      <c r="AN18" t="str">
+        <v/>
+      </c>
+      <c r="AO18" t="str">
+        <v/>
+      </c>
+      <c r="AP18" t="str">
+        <v/>
+      </c>
+      <c r="AQ18" t="str">
+        <v/>
+      </c>
+      <c r="AR18" t="str">
+        <v/>
+      </c>
+      <c r="AS18" t="str">
+        <v/>
+      </c>
+      <c r="AT18" t="str">
+        <v/>
+      </c>
+      <c r="AU18" t="str">
+        <v/>
+      </c>
+      <c r="AV18" t="str">
+        <v>DAD003</v>
+      </c>
+      <c r="AW18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>79</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E19" t="str">
+        <v>SPH20260330111213005</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-03-30 11:12:13</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19">
+        <v>749</v>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
+        <v/>
+      </c>
+      <c r="AA19" t="str">
+        <v/>
+      </c>
+      <c r="AB19" t="str">
+        <v/>
+      </c>
+      <c r="AC19" t="str">
+        <v/>
+      </c>
+      <c r="AD19" t="str">
+        <v/>
+      </c>
+      <c r="AE19" t="str">
+        <v/>
+      </c>
+      <c r="AF19" t="str">
+        <v/>
+      </c>
+      <c r="AG19" t="str">
+        <v/>
+      </c>
+      <c r="AH19" t="str">
+        <v/>
+      </c>
+      <c r="AI19" t="str">
+        <v/>
+      </c>
+      <c r="AJ19" t="str">
+        <v/>
+      </c>
+      <c r="AK19" t="str">
+        <v/>
+      </c>
+      <c r="AL19" t="str">
+        <v/>
+      </c>
+      <c r="AM19" t="str">
+        <v/>
+      </c>
+      <c r="AN19" t="str">
+        <v/>
+      </c>
+      <c r="AO19" t="str">
+        <v/>
+      </c>
+      <c r="AP19" t="str">
+        <v/>
+      </c>
+      <c r="AQ19" t="str">
+        <v/>
+      </c>
+      <c r="AR19" t="str">
+        <v/>
+      </c>
+      <c r="AS19" t="str">
+        <v/>
+      </c>
+      <c r="AT19" t="str">
+        <v/>
+      </c>
+      <c r="AU19" t="str">
+        <v/>
+      </c>
+      <c r="AV19" t="str">
+        <v>DAD003</v>
+      </c>
+      <c r="AW19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>80</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>视频号-靓仔台球</v>
+      </c>
+      <c r="E20" t="str">
+        <v>SPH20260331161857000</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-03-31 16:18:57</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20">
+        <v>338</v>
+      </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="str">
+        <v/>
+      </c>
+      <c r="AA20" t="str">
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <v/>
+      </c>
+      <c r="AE20" t="str">
+        <v/>
+      </c>
+      <c r="AF20" t="str">
+        <v/>
+      </c>
+      <c r="AG20" t="str">
+        <v/>
+      </c>
+      <c r="AH20" t="str">
+        <v/>
+      </c>
+      <c r="AI20" t="str">
+        <v/>
+      </c>
+      <c r="AJ20" t="str">
+        <v/>
+      </c>
+      <c r="AK20" t="str">
+        <v/>
+      </c>
+      <c r="AL20" t="str">
+        <v/>
+      </c>
+      <c r="AM20" t="str">
+        <v/>
+      </c>
+      <c r="AN20" t="str">
+        <v/>
+      </c>
+      <c r="AO20" t="str">
+        <v/>
+      </c>
+      <c r="AP20" t="str">
+        <v/>
+      </c>
+      <c r="AQ20" t="str">
+        <v/>
+      </c>
+      <c r="AR20" t="str">
+        <v/>
+      </c>
+      <c r="AS20" t="str">
+        <v/>
+      </c>
+      <c r="AT20" t="str">
+        <v/>
+      </c>
+      <c r="AU20" t="str">
+        <v/>
+      </c>
+      <c r="AV20" t="str">
+        <v>TA170</v>
+      </c>
+      <c r="AW20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>81</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E21" t="str">
+        <v>SPH20260331161857001</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-03-31 16:18:57</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21">
+        <v>98</v>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
+        <v/>
+      </c>
+      <c r="AA21" t="str">
+        <v/>
+      </c>
+      <c r="AB21" t="str">
+        <v/>
+      </c>
+      <c r="AC21" t="str">
+        <v/>
+      </c>
+      <c r="AD21" t="str">
+        <v/>
+      </c>
+      <c r="AE21" t="str">
+        <v/>
+      </c>
+      <c r="AF21" t="str">
+        <v/>
+      </c>
+      <c r="AG21" t="str">
+        <v/>
+      </c>
+      <c r="AH21" t="str">
+        <v/>
+      </c>
+      <c r="AI21" t="str">
+        <v/>
+      </c>
+      <c r="AJ21" t="str">
+        <v/>
+      </c>
+      <c r="AK21" t="str">
+        <v/>
+      </c>
+      <c r="AL21" t="str">
+        <v/>
+      </c>
+      <c r="AM21" t="str">
+        <v/>
+      </c>
+      <c r="AN21" t="str">
+        <v/>
+      </c>
+      <c r="AO21" t="str">
+        <v/>
+      </c>
+      <c r="AP21" t="str">
+        <v/>
+      </c>
+      <c r="AQ21" t="str">
+        <v/>
+      </c>
+      <c r="AR21" t="str">
+        <v/>
+      </c>
+      <c r="AS21" t="str">
+        <v/>
+      </c>
+      <c r="AT21" t="str">
+        <v/>
+      </c>
+      <c r="AU21" t="str">
+        <v/>
+      </c>
+      <c r="AV21" t="str">
+        <v>DAD011</v>
+      </c>
+      <c r="AW21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>82</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E22" t="str">
+        <v>SPH20260331161857002</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-03-31 16:18:57</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22">
+        <v>813</v>
+      </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="str">
+        <v/>
+      </c>
+      <c r="AA22" t="str">
+        <v/>
+      </c>
+      <c r="AB22" t="str">
+        <v/>
+      </c>
+      <c r="AC22" t="str">
+        <v/>
+      </c>
+      <c r="AD22" t="str">
+        <v/>
+      </c>
+      <c r="AE22" t="str">
+        <v/>
+      </c>
+      <c r="AF22" t="str">
+        <v/>
+      </c>
+      <c r="AG22" t="str">
+        <v/>
+      </c>
+      <c r="AH22" t="str">
+        <v/>
+      </c>
+      <c r="AI22" t="str">
+        <v/>
+      </c>
+      <c r="AJ22" t="str">
+        <v/>
+      </c>
+      <c r="AK22" t="str">
+        <v/>
+      </c>
+      <c r="AL22" t="str">
+        <v/>
+      </c>
+      <c r="AM22" t="str">
+        <v/>
+      </c>
+      <c r="AN22" t="str">
+        <v/>
+      </c>
+      <c r="AO22" t="str">
+        <v/>
+      </c>
+      <c r="AP22" t="str">
+        <v/>
+      </c>
+      <c r="AQ22" t="str">
+        <v/>
+      </c>
+      <c r="AR22" t="str">
+        <v/>
+      </c>
+      <c r="AS22" t="str">
+        <v/>
+      </c>
+      <c r="AT22" t="str">
+        <v/>
+      </c>
+      <c r="AU22" t="str">
+        <v/>
+      </c>
+      <c r="AV22" t="str">
+        <v>TA013</v>
+      </c>
+      <c r="AW22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>83</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>视频号-靓仔台球</v>
+      </c>
+      <c r="E23" t="str">
+        <v>SPH20260401154320000</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-04-01 15:43:20</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23">
+        <v>402</v>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
+        <v/>
+      </c>
+      <c r="AA23" t="str">
+        <v/>
+      </c>
+      <c r="AB23" t="str">
+        <v/>
+      </c>
+      <c r="AC23" t="str">
+        <v/>
+      </c>
+      <c r="AD23" t="str">
+        <v/>
+      </c>
+      <c r="AE23" t="str">
+        <v/>
+      </c>
+      <c r="AF23" t="str">
+        <v/>
+      </c>
+      <c r="AG23" t="str">
+        <v/>
+      </c>
+      <c r="AH23" t="str">
+        <v/>
+      </c>
+      <c r="AI23" t="str">
+        <v/>
+      </c>
+      <c r="AJ23" t="str">
+        <v/>
+      </c>
+      <c r="AK23" t="str">
+        <v/>
+      </c>
+      <c r="AL23" t="str">
+        <v/>
+      </c>
+      <c r="AM23" t="str">
+        <v/>
+      </c>
+      <c r="AN23" t="str">
+        <v/>
+      </c>
+      <c r="AO23" t="str">
+        <v/>
+      </c>
+      <c r="AP23" t="str">
+        <v/>
+      </c>
+      <c r="AQ23" t="str">
+        <v/>
+      </c>
+      <c r="AR23" t="str">
+        <v/>
+      </c>
+      <c r="AS23" t="str">
+        <v/>
+      </c>
+      <c r="AT23" t="str">
+        <v/>
+      </c>
+      <c r="AU23" t="str">
+        <v/>
+      </c>
+      <c r="AV23" t="str">
+        <v>TA013</v>
+      </c>
+      <c r="AW23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>84</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>视频号-王孟南台球教学</v>
+      </c>
+      <c r="E24" t="str">
+        <v>SPH20260401154320001</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-04-01 15:43:20</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
+      <c r="V24">
+        <v>784</v>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+      <c r="Z24" t="str">
+        <v/>
+      </c>
+      <c r="AA24" t="str">
+        <v/>
+      </c>
+      <c r="AB24" t="str">
+        <v/>
+      </c>
+      <c r="AC24" t="str">
+        <v/>
+      </c>
+      <c r="AD24" t="str">
+        <v/>
+      </c>
+      <c r="AE24" t="str">
+        <v/>
+      </c>
+      <c r="AF24" t="str">
+        <v/>
+      </c>
+      <c r="AG24" t="str">
+        <v/>
+      </c>
+      <c r="AH24" t="str">
+        <v/>
+      </c>
+      <c r="AI24" t="str">
+        <v/>
+      </c>
+      <c r="AJ24" t="str">
+        <v/>
+      </c>
+      <c r="AK24" t="str">
+        <v/>
+      </c>
+      <c r="AL24" t="str">
+        <v/>
+      </c>
+      <c r="AM24" t="str">
+        <v/>
+      </c>
+      <c r="AN24" t="str">
+        <v/>
+      </c>
+      <c r="AO24" t="str">
+        <v/>
+      </c>
+      <c r="AP24" t="str">
+        <v/>
+      </c>
+      <c r="AQ24" t="str">
+        <v/>
+      </c>
+      <c r="AR24" t="str">
+        <v/>
+      </c>
+      <c r="AS24" t="str">
+        <v/>
+      </c>
+      <c r="AT24" t="str">
+        <v/>
+      </c>
+      <c r="AU24" t="str">
+        <v/>
+      </c>
+      <c r="AV24" t="str">
+        <v>TB001</v>
+      </c>
+      <c r="AW24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>85</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>视频号-靓仔台球</v>
+      </c>
+      <c r="E25" t="str">
+        <v>SPH20260401154320002</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-04-01 15:43:20</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>待发货</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
+      <c r="V25">
+        <v>100</v>
+      </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <v/>
+      </c>
+      <c r="Z25" t="str">
+        <v/>
+      </c>
+      <c r="AA25" t="str">
+        <v/>
+      </c>
+      <c r="AB25" t="str">
+        <v/>
+      </c>
+      <c r="AC25" t="str">
+        <v/>
+      </c>
+      <c r="AD25" t="str">
+        <v/>
+      </c>
+      <c r="AE25" t="str">
+        <v/>
+      </c>
+      <c r="AF25" t="str">
+        <v/>
+      </c>
+      <c r="AG25" t="str">
+        <v/>
+      </c>
+      <c r="AH25" t="str">
+        <v/>
+      </c>
+      <c r="AI25" t="str">
+        <v/>
+      </c>
+      <c r="AJ25" t="str">
+        <v/>
+      </c>
+      <c r="AK25" t="str">
+        <v/>
+      </c>
+      <c r="AL25" t="str">
+        <v/>
+      </c>
+      <c r="AM25" t="str">
+        <v/>
+      </c>
+      <c r="AN25" t="str">
+        <v/>
+      </c>
+      <c r="AO25" t="str">
+        <v/>
+      </c>
+      <c r="AP25" t="str">
+        <v/>
+      </c>
+      <c r="AQ25" t="str">
+        <v/>
+      </c>
+      <c r="AR25" t="str">
+        <v/>
+      </c>
+      <c r="AS25" t="str">
+        <v/>
+      </c>
+      <c r="AT25" t="str">
+        <v/>
+      </c>
+      <c r="AU25" t="str">
+        <v/>
+      </c>
+      <c r="AV25" t="str">
+        <v>DAD005</v>
+      </c>
+      <c r="AW25" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AV11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q6"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>店铺</v>
-      </c>
-      <c r="B1" t="str">
-        <v>售后单号</v>
-      </c>
-      <c r="C1" t="str">
-        <v>订单号</v>
-      </c>
-      <c r="D1" t="str">
-        <v>商品单号</v>
-      </c>
-      <c r="E1" t="str">
-        <v>商品名称</v>
-      </c>
-      <c r="F1" t="str">
-        <v>商品ID</v>
-      </c>
-      <c r="G1" t="str">
-        <v>应付金额（元）</v>
-      </c>
-      <c r="H1" t="str">
-        <v>商品运费（元）</v>
-      </c>
-      <c r="I1" t="str">
-        <v>支付优惠（元）</v>
-      </c>
-      <c r="J1" t="str">
-        <v>商品税费（元）</v>
-      </c>
-      <c r="K1" t="str">
-        <v>商品发货状态</v>
-      </c>
-      <c r="L1" t="str">
-        <v>售后类型</v>
-      </c>
-      <c r="M1" t="str">
-        <v>退商品金额（元）</v>
-      </c>
-      <c r="N1" t="str">
-        <v>退运费金额（元）</v>
-      </c>
-      <c r="O1" t="str">
-        <v>退支付优惠（元）</v>
-      </c>
-      <c r="P1" t="str">
-        <v>退税费金额（元）</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>售后状态</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>抖店-靓仔甄选台球店</v>
-      </c>
-      <c r="B2" t="str">
-        <v>147381574123432506</v>
-      </c>
-      <c r="C2" t="str">
-        <v>6924613001685072899</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2">
-        <v>2980</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>同意退款，退款成功</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>抖店-靓仔甄选台球店</v>
-      </c>
-      <c r="B3" t="str">
-        <v>147384742635630775</v>
-      </c>
-      <c r="C3" t="str">
-        <v>6924673349722799584</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3">
-        <v>990</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v>同意退款，退款成功</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>抖店-靓仔甄选台球店</v>
-      </c>
-      <c r="B4" t="str">
-        <v>147384743626339363</v>
-      </c>
-      <c r="C4" t="str">
-        <v>6951083596125443783</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4">
-        <v>990</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v>同意退款，退款成功</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>抖店-靓仔甄选台球店</v>
-      </c>
-      <c r="B5" t="str">
-        <v>147384744681158124</v>
-      </c>
-      <c r="C5" t="str">
-        <v>6924666887718338336</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5">
-        <v>990</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v>同意退款，退款成功</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>抖店-靓仔甄选台球店</v>
-      </c>
-      <c r="B6" t="str">
-        <v>147384744632139294</v>
-      </c>
-      <c r="C6" t="str">
-        <v>6951074755619198383</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6">
-        <v>990</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v>同意退款，退款成功</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>店铺</v>
-      </c>
-      <c r="B1" t="str">
-        <v>售后单号</v>
-      </c>
-      <c r="C1" t="str">
-        <v>订单编号</v>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-      <c r="G1" t="str">
-        <v/>
-      </c>
-      <c r="H1" t="str">
-        <v/>
-      </c>
-      <c r="I1" t="str">
-        <v/>
-      </c>
-      <c r="J1" t="str">
-        <v/>
-      </c>
-      <c r="K1" t="str">
-        <v/>
-      </c>
-      <c r="L1" t="str">
-        <v/>
-      </c>
-      <c r="M1" t="str">
-        <v/>
-      </c>
-      <c r="N1" t="str">
-        <v/>
-      </c>
-      <c r="O1" t="str">
-        <v/>
-      </c>
-      <c r="P1" t="str">
-        <v>退款金额</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>售后状态</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>快手-王孟南台球教学</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2608601682584322</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2608600564020322</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2">
-        <v>1980</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>售后成功</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>快手-王孟南台球教学</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2608602000067509</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2608601603272509</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3">
-        <v>1980</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>售后成功</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>快手-王孟南台球教学</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2608601760851784</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2608600160037784</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4">
-        <v>990</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>售后成功</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AW25"/>
   </ignoredErrors>
 </worksheet>
 </file>